--- a/publications.xlsx
+++ b/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ghe/Documents/GitHub/quarto-academic-website-template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\OneDrive\Documents\GitHub\gafrm.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DFC406-A80B-A440-998C-5F77B7D5D078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -249,14 +249,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,31 +559,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="55" style="1" customWidth="1"/>
     <col min="3" max="3" width="6" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" customWidth="1"/>
     <col min="5" max="6" width="70" style="1" customWidth="1"/>
     <col min="7" max="7" width="32" style="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="1" customWidth="1"/>
     <col min="9" max="9" width="7" style="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="1" customWidth="1"/>
     <col min="11" max="11" width="40" style="1" customWidth="1"/>
-    <col min="12" max="12" width="50.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="50.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="55" style="1" customWidth="1"/>
     <col min="14" max="14" width="35" style="1" customWidth="1"/>
     <col min="15" max="15" width="38" style="1" customWidth="1"/>
-    <col min="16" max="16" width="51.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="51.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="20" width="38" style="1" customWidth="1"/>
     <col min="21" max="23" width="80" style="1" customWidth="1"/>
-    <col min="24" max="24" width="41.5" style="1" customWidth="1"/>
-    <col min="25" max="26" width="8.83203125" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.83203125" style="1"/>
+    <col min="24" max="24" width="41.42578125" style="1" customWidth="1"/>
+    <col min="25" max="26" width="8.85546875" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +657,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -698,7 +697,7 @@
       <c r="P2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" t="s">
         <v>41</v>
       </c>
       <c r="S2" s="1">
@@ -720,7 +719,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
